--- a/logs/experiments_not_systematic/thesis_final_optimization/results_changing_map.xlsx
+++ b/logs/experiments_not_systematic/thesis_final_optimization/results_changing_map.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/thesis_final_optimization/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/experiments_not_systematic/thesis_final_optimization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="11_4BA110ACD3A05FE1448A1AD04B5ED87656CD4391" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5C9D4DB-4807-4916-92B7-9C551017C4F8}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="11_4BA110ACD3A05FE1448A1AD04B5ED87656CD4391" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE6D80AF-EE14-4893-AC34-A2F9E999AC6E}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-5580" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,13 +18,13 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId3"/>
+    <pivotCache cacheId="3" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="130">
   <si>
     <t>date</t>
   </si>
@@ -1392,8 +1392,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5B4F823-F791-4AA9-BEDA-45CA4C4B15FC}" name="TablaDinámica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A1:L27" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5B4F823-F791-4AA9-BEDA-45CA4C4B15FC}" name="TablaDinámica1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A1:L33" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="76">
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -1458,7 +1458,7 @@
       <items count="4">
         <item x="0"/>
         <item x="1"/>
-        <item sd="0" x="2"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1541,7 +1541,7 @@
     <field x="31"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="26">
+  <rowItems count="32">
     <i>
       <x/>
     </i>
@@ -1616,6 +1616,24 @@
     </i>
     <i>
       <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="2">
+      <x v="3"/>
+    </i>
+    <i r="3">
+      <x v="2"/>
+    </i>
+    <i r="4">
+      <x v="3"/>
+    </i>
+    <i r="5">
+      <x v="2"/>
+    </i>
+    <i r="6">
+      <x/>
     </i>
     <i t="grand">
       <x/>
@@ -3952,10 +3970,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05910FD6-0987-4D4C-84BD-F3900F2A32F6}">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="54.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="67.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
@@ -4959,40 +4977,268 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="5">
+        <v>3</v>
+      </c>
+      <c r="B27" s="11">
+        <v>0.82385352498761921</v>
+      </c>
+      <c r="C27" s="11">
+        <v>0.23103670181798511</v>
+      </c>
+      <c r="D27" s="11">
+        <v>0.65910444269139501</v>
+      </c>
+      <c r="E27" s="11">
+        <v>0.1435394443367185</v>
+      </c>
+      <c r="F27" s="11">
+        <v>0.92207657463165105</v>
+      </c>
+      <c r="G27" s="11">
+        <v>0.4643919388436909</v>
+      </c>
+      <c r="H27" s="11">
+        <v>0.90193691076609406</v>
+      </c>
+      <c r="I27" s="11">
+        <v>0.41362254028166678</v>
+      </c>
+      <c r="J27" s="11">
+        <v>0.64419630755713964</v>
+      </c>
+      <c r="K27" s="11">
+        <v>-6.5479283638410157E-2</v>
+      </c>
+      <c r="L27" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" s="11">
+        <v>0.82385352498761921</v>
+      </c>
+      <c r="C28" s="11">
+        <v>0.23103670181798511</v>
+      </c>
+      <c r="D28" s="11">
+        <v>0.65910444269139501</v>
+      </c>
+      <c r="E28" s="11">
+        <v>0.1435394443367185</v>
+      </c>
+      <c r="F28" s="11">
+        <v>0.92207657463165105</v>
+      </c>
+      <c r="G28" s="11">
+        <v>0.4643919388436909</v>
+      </c>
+      <c r="H28" s="11">
+        <v>0.90193691076609406</v>
+      </c>
+      <c r="I28" s="11">
+        <v>0.41362254028166678</v>
+      </c>
+      <c r="J28" s="11">
+        <v>0.64419630755713964</v>
+      </c>
+      <c r="K28" s="11">
+        <v>-6.5479283638410157E-2</v>
+      </c>
+      <c r="L28" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="11">
+        <v>0.82385352498761921</v>
+      </c>
+      <c r="C29" s="11">
+        <v>0.23103670181798511</v>
+      </c>
+      <c r="D29" s="11">
+        <v>0.65910444269139501</v>
+      </c>
+      <c r="E29" s="11">
+        <v>0.1435394443367185</v>
+      </c>
+      <c r="F29" s="11">
+        <v>0.92207657463165105</v>
+      </c>
+      <c r="G29" s="11">
+        <v>0.4643919388436909</v>
+      </c>
+      <c r="H29" s="11">
+        <v>0.90193691076609406</v>
+      </c>
+      <c r="I29" s="11">
+        <v>0.41362254028166678</v>
+      </c>
+      <c r="J29" s="11">
+        <v>0.64419630755713964</v>
+      </c>
+      <c r="K29" s="11">
+        <v>-6.5479283638410157E-2</v>
+      </c>
+      <c r="L29" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" s="11">
+        <v>0.82385352498761921</v>
+      </c>
+      <c r="C30" s="11">
+        <v>0.23103670181798511</v>
+      </c>
+      <c r="D30" s="11">
+        <v>0.65910444269139501</v>
+      </c>
+      <c r="E30" s="11">
+        <v>0.1435394443367185</v>
+      </c>
+      <c r="F30" s="11">
+        <v>0.92207657463165105</v>
+      </c>
+      <c r="G30" s="11">
+        <v>0.4643919388436909</v>
+      </c>
+      <c r="H30" s="11">
+        <v>0.90193691076609406</v>
+      </c>
+      <c r="I30" s="11">
+        <v>0.41362254028166678</v>
+      </c>
+      <c r="J30" s="11">
+        <v>0.64419630755713964</v>
+      </c>
+      <c r="K30" s="11">
+        <v>-6.5479283638410157E-2</v>
+      </c>
+      <c r="L30" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B31" s="11">
+        <v>0.82385352498761921</v>
+      </c>
+      <c r="C31" s="11">
+        <v>0.23103670181798511</v>
+      </c>
+      <c r="D31" s="11">
+        <v>0.65910444269139501</v>
+      </c>
+      <c r="E31" s="11">
+        <v>0.1435394443367185</v>
+      </c>
+      <c r="F31" s="11">
+        <v>0.92207657463165105</v>
+      </c>
+      <c r="G31" s="11">
+        <v>0.4643919388436909</v>
+      </c>
+      <c r="H31" s="11">
+        <v>0.90193691076609406</v>
+      </c>
+      <c r="I31" s="11">
+        <v>0.41362254028166678</v>
+      </c>
+      <c r="J31" s="11">
+        <v>0.64419630755713964</v>
+      </c>
+      <c r="K31" s="11">
+        <v>-6.5479283638410157E-2</v>
+      </c>
+      <c r="L31" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="10">
+        <v>1</v>
+      </c>
+      <c r="B32" s="11">
+        <v>0.82385352498761921</v>
+      </c>
+      <c r="C32" s="11">
+        <v>0.23103670181798511</v>
+      </c>
+      <c r="D32" s="11">
+        <v>0.65910444269139501</v>
+      </c>
+      <c r="E32" s="11">
+        <v>0.1435394443367185</v>
+      </c>
+      <c r="F32" s="11">
+        <v>0.92207657463165105</v>
+      </c>
+      <c r="G32" s="11">
+        <v>0.4643919388436909</v>
+      </c>
+      <c r="H32" s="11">
+        <v>0.90193691076609406</v>
+      </c>
+      <c r="I32" s="11">
+        <v>0.41362254028166678</v>
+      </c>
+      <c r="J32" s="11">
+        <v>0.64419630755713964</v>
+      </c>
+      <c r="K32" s="11">
+        <v>-6.5479283638410157E-2</v>
+      </c>
+      <c r="L32" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B33" s="11">
         <v>0.74426823118492924</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C33" s="11">
         <v>-0.6404360628858925</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D33" s="11">
         <v>0.59312765396400224</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E33" s="11">
         <v>-0.92339963168327832</v>
       </c>
-      <c r="F27" s="11">
+      <c r="F33" s="11">
         <v>0.89304087017746436</v>
       </c>
-      <c r="G27" s="11">
+      <c r="G33" s="11">
         <v>-0.42998595067817319</v>
       </c>
-      <c r="H27" s="11">
+      <c r="H33" s="11">
         <v>0.86036359975677146</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I33" s="11">
         <v>-0.2130628847293822</v>
       </c>
-      <c r="J27" s="11">
+      <c r="J33" s="11">
         <v>0.59159996993543618</v>
       </c>
-      <c r="K27" s="11">
+      <c r="K33" s="11">
         <v>-0.41641134459797274</v>
       </c>
-      <c r="L27" s="11">
+      <c r="L33" s="11">
         <v>7</v>
       </c>
     </row>
